--- a/AAII_Financials/Quarterly/SDXAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SDXAY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="92">
   <si>
     <t>SDXAY</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E7" s="2">
         <v>45169</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45077</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44985</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44895</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44804</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44712</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44620</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44530</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44439</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44347</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44255</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44165</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44074</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43982</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43890</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43799</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43708</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43616</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43524</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43434</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43343</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43251</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43159</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43069</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42978</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42886</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42794</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42704</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>11448900</v>
+        <v>6840900</v>
       </c>
       <c r="E8" s="3">
-        <v>6538200</v>
+        <v>11481600</v>
       </c>
       <c r="F8" s="3">
-        <v>13112200</v>
+        <v>6556900</v>
       </c>
       <c r="G8" s="3">
-        <v>6868100</v>
+        <v>13149700</v>
       </c>
       <c r="H8" s="3">
-        <v>10851100</v>
+        <v>6887700</v>
       </c>
       <c r="I8" s="3">
-        <v>5992500</v>
+        <v>10882100</v>
       </c>
       <c r="J8" s="3">
+        <v>6009600</v>
+      </c>
+      <c r="K8" s="3">
         <v>11134300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5706700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9512300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4744100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8773800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4420500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7918100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4266500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13201400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7093200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>13363400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6684300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>13212000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6708200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11202300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5748000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11548600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5960000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11291700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6002600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>12482300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6398400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>11326100</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>10406200</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3">
-        <v>11203700</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3">
-        <v>9781300</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3">
+        <v>10436000</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="3">
+        <v>11235700</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="3">
+        <v>9809200</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K9" s="3">
         <v>9539300</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="3">
         <v>8174700</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="3">
         <v>7569200</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3">
         <v>7138700</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3">
         <v>11250400</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="3">
         <v>11440200</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W9" s="3">
         <v>11264600</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="3">
         <v>9540900</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="3">
         <v>9768000</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB9" s="3">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC9" s="3">
         <v>9561600</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD9" s="3">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="3">
         <v>10484500</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF9" s="3">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="3">
         <v>9595900</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>1042700</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1908500</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1069800</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1045700</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1914000</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1072900</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K10" s="3">
         <v>1595000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M10" s="3">
         <v>1337500</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="3">
         <v>1204500</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3">
         <v>779500</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3">
         <v>1951100</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U10" s="3">
         <v>1923200</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W10" s="3">
         <v>1947400</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="3">
         <v>1661400</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA10" s="3">
         <v>1780600</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB10" s="3">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC10" s="3">
         <v>1730100</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD10" s="3">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="3">
         <v>1997800</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF10" s="3">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="3">
         <v>1730200</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,73 +1298,76 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>89000</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
+        <v>44600</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
         <v>9800</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3">
-        <v>-58600</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-58800</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>6500</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
         <v>88300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3">
         <v>110200</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
         <v>438000</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
         <v>41800</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
         <v>41600</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="3">
         <v>27500</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>5</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>5</v>
@@ -1359,86 +1378,89 @@
       <c r="AA14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE14" s="3">
         <v>12900</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="3">
         <v>15200</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="3">
+      <c r="F15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="3">
         <v>23900</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H15" s="3">
+      <c r="H15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I15" s="3">
         <v>17400</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="J15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K15" s="3">
         <v>21700</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L15" s="3">
+      <c r="L15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M15" s="3">
         <v>12900</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N15" s="3">
+      <c r="N15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O15" s="3">
         <v>21400</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P15" s="3">
+      <c r="P15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="3">
         <v>4200</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R15" s="3">
+      <c r="R15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S15" s="3">
         <v>22600</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="T15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U15" s="3">
         <v>51400</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V15" s="3">
+      <c r="V15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W15" s="3">
         <v>51400</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
-      </c>
       <c r="X15" s="3">
         <v>0</v>
       </c>
@@ -1466,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>11248200</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="3">
-        <v>12394000</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H17" s="3">
-        <v>10552700</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3">
+        <v>11280300</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3">
+        <v>12429400</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="3">
+        <v>10582900</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="3">
         <v>10551600</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M17" s="3">
         <v>9293600</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O17" s="3">
         <v>8634900</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="3">
         <v>8493100</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="3">
         <v>12502500</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="T17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U17" s="3">
         <v>12774200</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="V17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W17" s="3">
         <v>12520600</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="X17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y17" s="3">
         <v>10711600</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="Z17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA17" s="3">
         <v>10927100</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB17" s="3">
+      <c r="AB17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC17" s="3">
         <v>10615100</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD17" s="3">
+      <c r="AD17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE17" s="3">
         <v>11807400</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF17" s="3">
+      <c r="AF17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG17" s="3">
         <v>10769700</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>200700</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="3">
-        <v>718300</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H18" s="3">
-        <v>298400</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3">
+        <v>201300</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3">
+        <v>720300</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="3">
+        <v>299200</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="3">
         <v>582600</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M18" s="3">
         <v>218600</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O18" s="3">
         <v>138800</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-575000</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="3">
         <v>698900</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U18" s="3">
         <v>589200</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W18" s="3">
         <v>691400</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="3">
         <v>490700</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA18" s="3">
         <v>621600</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC18" s="3">
         <v>676600</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE18" s="3">
         <v>674900</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG18" s="3">
         <v>556400</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,120 +1747,124 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>32500</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="3">
-        <v>33600</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3">
+        <v>32600</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3">
+        <v>33700</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3">
         <v>25000</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1100</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>3200</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O20" s="3">
         <v>4100</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-153600</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" s="3">
         <v>9000</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U20" s="3">
         <v>22000</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W20" s="3">
         <v>8400</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y20" s="3">
         <v>12200</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA20" s="3">
         <v>12300</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AD20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE20" s="3">
         <v>5900</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
+      <c r="E21" s="3">
+        <v>732300</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
+      <c r="G21" s="3">
+        <v>1040200</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
+      <c r="I21" s="3">
+        <v>893300</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>5</v>
@@ -1836,347 +1872,359 @@
       <c r="K21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M21" s="3">
         <v>869100</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
         <v>201400</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="3">
         <v>830500</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W21" s="3">
         <v>922300</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3">
         <v>681200</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA21" s="3">
         <v>809000</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC21" s="3">
         <v>833600</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE21" s="3">
         <v>845100</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG21" s="3">
         <v>699600</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>86800</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="3">
-        <v>85700</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H22" s="3">
-        <v>60800</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3">
+        <v>87000</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3">
+        <v>86000</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3">
+        <v>60900</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="3">
         <v>56400</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" s="3">
         <v>61400</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O22" s="3">
         <v>53100</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="3">
         <v>77800</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S22" s="3">
         <v>80200</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U22" s="3">
         <v>75900</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W22" s="3">
         <v>70600</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y22" s="3">
         <v>62000</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA22" s="3">
         <v>60600</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC22" s="3">
         <v>51600</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD22" s="3">
+      <c r="AD22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE22" s="3">
         <v>56300</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF22" s="3">
+      <c r="AF22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG22" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>146500</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="3">
-        <v>666200</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H23" s="3">
-        <v>262600</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3">
+        <v>146900</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="3">
+        <v>668100</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" s="3">
+        <v>263300</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="3">
         <v>525100</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M23" s="3">
         <v>160500</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O23" s="3">
         <v>89800</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-806400</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="R23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" s="3">
         <v>627800</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="T23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U23" s="3">
         <v>535300</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="V23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W23" s="3">
         <v>629200</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="X23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y23" s="3">
         <v>440800</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="Z23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA23" s="3">
         <v>573300</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB23" s="3">
+      <c r="AB23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC23" s="3">
         <v>623800</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD23" s="3">
+      <c r="AD23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE23" s="3">
         <v>624500</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF23" s="3">
+      <c r="AF23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG23" s="3">
         <v>486000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3">
         <v>16300</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="3">
-        <v>180100</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H24" s="3">
-        <v>76000</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3">
+        <v>180600</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3">
+        <v>76200</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
         <v>147600</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M24" s="3">
         <v>51700</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O24" s="3">
         <v>54100</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-65400</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="R24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S24" s="3">
         <v>181800</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="T24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U24" s="3">
         <v>154300</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="V24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W24" s="3">
         <v>180600</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="X24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y24" s="3">
         <v>126300</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="Z24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA24" s="3">
         <v>147000</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB24" s="3">
+      <c r="AB24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC24" s="3">
         <v>191900</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD24" s="3">
+      <c r="AD24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE24" s="3">
         <v>201900</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF24" s="3">
+      <c r="AF24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG24" s="3">
         <v>150200</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>130200</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" s="3">
-        <v>486100</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H26" s="3">
-        <v>186600</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3">
+        <v>130600</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3">
+        <v>487500</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="3">
+        <v>187200</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26" s="3">
         <v>377600</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M26" s="3">
         <v>108800</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O26" s="3">
         <v>35700</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-741100</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S26" s="3">
         <v>446000</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="T26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U26" s="3">
         <v>381000</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W26" s="3">
         <v>448600</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="X26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y26" s="3">
         <v>314600</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="Z26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA26" s="3">
         <v>426400</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB26" s="3">
+      <c r="AB26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC26" s="3">
         <v>432000</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD26" s="3">
+      <c r="AD26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE26" s="3">
         <v>422600</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF26" s="3">
+      <c r="AF26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG26" s="3">
         <v>335700</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>130200</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" s="3">
-        <v>477400</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H27" s="3">
-        <v>192000</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3">
+        <v>130600</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3">
+        <v>478800</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="3">
+        <v>192600</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K27" s="3">
         <v>365600</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M27" s="3">
         <v>114200</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O27" s="3">
         <v>33700</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-719300</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" s="3">
         <v>426800</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="T27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U27" s="3">
         <v>368700</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W27" s="3">
         <v>435400</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="X27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y27" s="3">
         <v>309000</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="Z27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA27" s="3">
         <v>417400</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB27" s="3">
+      <c r="AB27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC27" s="3">
         <v>420700</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD27" s="3">
+      <c r="AD27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE27" s="3">
         <v>408500</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF27" s="3">
+      <c r="AF27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG27" s="3">
         <v>326300</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,16 +2600,19 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>253900</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
+      <c r="D29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" s="3">
+        <v>254600</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>5</v>
@@ -2560,17 +2620,17 @@
       <c r="G29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H29" s="3">
-        <v>196400</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>5</v>
+      <c r="H29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I29" s="3">
+        <v>196900</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-32500</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-33600</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-32600</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3">
         <v>-25000</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>1100</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>-3200</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O32" s="3">
         <v>-4100</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3">
         <v>153600</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S32" s="3">
         <v>-9000</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U32" s="3">
         <v>-22000</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W32" s="3">
         <v>-8400</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-12200</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-12300</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC32" s="3">
         <v>1100</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AD32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG32" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>384100</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" s="3">
-        <v>477400</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H33" s="3">
-        <v>388400</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3">
+        <v>385200</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="3">
+        <v>478800</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" s="3">
+        <v>389500</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K33" s="3">
         <v>365600</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M33" s="3">
         <v>114200</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O33" s="3">
         <v>33700</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-719300</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S33" s="3">
         <v>426800</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="T33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U33" s="3">
         <v>368700</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W33" s="3">
         <v>435400</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="X33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y33" s="3">
         <v>309000</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="Z33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA33" s="3">
         <v>417400</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB33" s="3">
+      <c r="AB33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC33" s="3">
         <v>420700</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD33" s="3">
+      <c r="AD33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE33" s="3">
         <v>408500</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF33" s="3">
+      <c r="AF33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG33" s="3">
         <v>326300</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>384100</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" s="3">
-        <v>477400</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H35" s="3">
-        <v>388400</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="3">
+        <v>385200</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3">
+        <v>478800</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" s="3">
+        <v>389500</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3">
         <v>365600</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M35" s="3">
         <v>114200</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O35" s="3">
         <v>33700</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-719300</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S35" s="3">
         <v>426800</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="T35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U35" s="3">
         <v>368700</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W35" s="3">
         <v>435400</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="X35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y35" s="3">
         <v>309000</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="Z35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA35" s="3">
         <v>417400</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB35" s="3">
+      <c r="AB35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC35" s="3">
         <v>420700</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD35" s="3">
+      <c r="AD35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE35" s="3">
         <v>408500</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF35" s="3">
+      <c r="AF35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG35" s="3">
         <v>326300</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E38" s="2">
         <v>45169</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45077</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44985</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44895</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44804</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44712</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44620</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44530</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44439</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44347</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44255</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44165</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44074</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43982</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43890</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43799</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43708</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43616</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43524</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43434</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43343</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43251</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43159</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43069</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42978</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42886</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42794</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42704</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,28 +3437,29 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2160200</v>
+        <v>2166400</v>
       </c>
       <c r="E41" s="3">
-        <v>2218800</v>
+        <v>2225200</v>
       </c>
       <c r="F41" s="3">
-        <v>2930600</v>
+        <v>2939000</v>
       </c>
       <c r="G41" s="3">
-        <v>2354500</v>
+        <v>2361200</v>
       </c>
       <c r="H41" s="3">
-        <v>3482900</v>
-      </c>
-      <c r="I41" s="3">
-        <v>2019200</v>
+        <v>3492800</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>5</v>
@@ -3399,73 +3485,76 @@
       <c r="Q41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R41" s="3">
+      <c r="R41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S41" s="3">
         <v>1505100</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T41" s="3">
+      <c r="T41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U41" s="3">
         <v>1723600</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V41" s="3">
+      <c r="V41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W41" s="3">
         <v>1824200</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X41" s="3">
+      <c r="X41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y41" s="3">
         <v>1441000</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z41" s="3">
+      <c r="Z41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA41" s="3">
         <v>1216200</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB41" s="3">
+      <c r="AB41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC41" s="3">
         <v>1792900</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD41" s="3">
+      <c r="AD41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE41" s="3">
         <v>1472000</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF41" s="3">
+      <c r="AF41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG41" s="3">
         <v>1199600</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>117200</v>
+        <v>117500</v>
       </c>
       <c r="E42" s="3">
-        <v>696600</v>
+        <v>698600</v>
       </c>
       <c r="F42" s="3">
-        <v>630400</v>
+        <v>632200</v>
       </c>
       <c r="G42" s="3">
-        <v>530600</v>
+        <v>532100</v>
       </c>
       <c r="H42" s="3">
-        <v>399300</v>
-      </c>
-      <c r="I42" s="3">
-        <v>421000</v>
+        <v>400400</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>5</v>
@@ -3491,73 +3580,76 @@
       <c r="Q42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R42" s="3">
+      <c r="R42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S42" s="3">
         <v>465200</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T42" s="3">
+      <c r="T42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U42" s="3">
         <v>529200</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V42" s="3">
+      <c r="V42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W42" s="3">
         <v>553800</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X42" s="3">
+      <c r="X42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y42" s="3">
         <v>444100</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z42" s="3">
+      <c r="Z42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA42" s="3">
         <v>526200</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB42" s="3">
+      <c r="AB42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC42" s="3">
         <v>507100</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD42" s="3">
+      <c r="AD42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE42" s="3">
         <v>563400</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF42" s="3">
+      <c r="AF42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG42" s="3">
         <v>466000</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3955900</v>
+        <v>3967200</v>
       </c>
       <c r="E43" s="3">
-        <v>6319000</v>
+        <v>6337100</v>
       </c>
       <c r="F43" s="3">
-        <v>5684300</v>
+        <v>5700600</v>
       </c>
       <c r="G43" s="3">
-        <v>5746200</v>
+        <v>5762600</v>
       </c>
       <c r="H43" s="3">
-        <v>4805500</v>
-      </c>
-      <c r="I43" s="3">
-        <v>5034400</v>
+        <v>4819200</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>5</v>
@@ -3583,73 +3675,76 @@
       <c r="Q43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R43" s="3">
+      <c r="R43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S43" s="3">
         <v>6273300</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T43" s="3">
+      <c r="T43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U43" s="3">
         <v>5819900</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V43" s="3">
+      <c r="V43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W43" s="3">
         <v>6270500</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X43" s="3">
+      <c r="X43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y43" s="3">
         <v>4759400</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z43" s="3">
+      <c r="Z43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA43" s="3">
         <v>5479800</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB43" s="3">
+      <c r="AB43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC43" s="3">
         <v>4751600</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD43" s="3">
+      <c r="AD43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE43" s="3">
         <v>6121400</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF43" s="3">
+      <c r="AF43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG43" s="3">
         <v>4899500</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>351500</v>
+        <v>352500</v>
       </c>
       <c r="E44" s="3">
-        <v>379800</v>
+        <v>380800</v>
       </c>
       <c r="F44" s="3">
-        <v>381900</v>
+        <v>383000</v>
       </c>
       <c r="G44" s="3">
-        <v>326600</v>
+        <v>327500</v>
       </c>
       <c r="H44" s="3">
-        <v>277800</v>
-      </c>
-      <c r="I44" s="3">
-        <v>265800</v>
+        <v>278600</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>5</v>
@@ -3675,73 +3770,76 @@
       <c r="Q44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R44" s="3">
+      <c r="R44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S44" s="3">
         <v>337600</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T44" s="3">
+      <c r="T44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U44" s="3">
         <v>360100</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V44" s="3">
+      <c r="V44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W44" s="3">
         <v>346900</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X44" s="3">
+      <c r="X44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y44" s="3">
         <v>310100</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z44" s="3">
+      <c r="Z44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA44" s="3">
         <v>314200</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB44" s="3">
+      <c r="AB44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC44" s="3">
         <v>288400</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD44" s="3">
+      <c r="AD44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE44" s="3">
         <v>327500</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF44" s="3">
+      <c r="AF44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG44" s="3">
         <v>314600</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5771100</v>
+        <v>5787600</v>
       </c>
       <c r="E45" s="3">
-        <v>1404000</v>
+        <v>1408000</v>
       </c>
       <c r="F45" s="3">
-        <v>1369300</v>
+        <v>1373200</v>
       </c>
       <c r="G45" s="3">
-        <v>1447400</v>
+        <v>1451500</v>
       </c>
       <c r="H45" s="3">
-        <v>1485400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1254300</v>
+        <v>1489600</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>5</v>
@@ -3767,73 +3865,76 @@
       <c r="Q45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R45" s="3">
+      <c r="R45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S45" s="3">
         <v>1129100</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T45" s="3">
+      <c r="T45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U45" s="3">
         <v>1381800</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W45" s="3">
         <v>1252400</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X45" s="3">
+      <c r="X45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y45" s="3">
         <v>1170700</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z45" s="3">
+      <c r="Z45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA45" s="3">
         <v>1088300</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB45" s="3">
+      <c r="AB45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC45" s="3">
         <v>1027700</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD45" s="3">
+      <c r="AD45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE45" s="3">
         <v>1014200</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF45" s="3">
+      <c r="AF45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG45" s="3">
         <v>937900</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>12356000</v>
+        <v>12391300</v>
       </c>
       <c r="E46" s="3">
-        <v>11018200</v>
+        <v>11049700</v>
       </c>
       <c r="F46" s="3">
-        <v>10996500</v>
+        <v>11027900</v>
       </c>
       <c r="G46" s="3">
-        <v>10405200</v>
+        <v>10434900</v>
       </c>
       <c r="H46" s="3">
-        <v>10450700</v>
-      </c>
-      <c r="I46" s="3">
-        <v>8994700</v>
+        <v>10480600</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>5</v>
@@ -3859,73 +3960,76 @@
       <c r="Q46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R46" s="3">
+      <c r="R46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S46" s="3">
         <v>9710300</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T46" s="3">
+      <c r="T46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U46" s="3">
         <v>9814600</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V46" s="3">
+      <c r="V46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W46" s="3">
         <v>10247800</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X46" s="3">
+      <c r="X46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y46" s="3">
         <v>8125400</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z46" s="3">
+      <c r="Z46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA46" s="3">
         <v>8624700</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB46" s="3">
+      <c r="AB46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC46" s="3">
         <v>8367800</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD46" s="3">
+      <c r="AD46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE46" s="3">
         <v>9498500</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF46" s="3">
+      <c r="AF46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG46" s="3">
         <v>7817600</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1979000</v>
+        <v>1984700</v>
       </c>
       <c r="E47" s="3">
-        <v>2052800</v>
+        <v>2058700</v>
       </c>
       <c r="F47" s="3">
-        <v>1915000</v>
+        <v>1920500</v>
       </c>
       <c r="G47" s="3">
-        <v>1670900</v>
+        <v>1675700</v>
       </c>
       <c r="H47" s="3">
-        <v>1472300</v>
-      </c>
-      <c r="I47" s="3">
-        <v>1479900</v>
+        <v>1476600</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>5</v>
@@ -3951,73 +4055,76 @@
       <c r="Q47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R47" s="3">
+      <c r="R47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S47" s="3">
         <v>1849500</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T47" s="3">
+      <c r="T47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U47" s="3">
         <v>2066600</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W47" s="3">
         <v>1876800</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X47" s="3">
+      <c r="X47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y47" s="3">
         <v>920400</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z47" s="3">
+      <c r="Z47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA47" s="3">
         <v>884100</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB47" s="3">
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC47" s="3">
         <v>896500</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD47" s="3">
+      <c r="AD47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE47" s="3">
         <v>934400</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF47" s="3">
+      <c r="AF47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG47" s="3">
         <v>917900</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1407200</v>
+        <v>1411300</v>
       </c>
       <c r="E48" s="3">
-        <v>1468000</v>
+        <v>1472200</v>
       </c>
       <c r="F48" s="3">
-        <v>1524400</v>
+        <v>1528800</v>
       </c>
       <c r="G48" s="3">
-        <v>1490800</v>
+        <v>1495000</v>
       </c>
       <c r="H48" s="3">
-        <v>1479900</v>
-      </c>
-      <c r="I48" s="3">
-        <v>1898800</v>
+        <v>1484200</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
@@ -4043,73 +4150,76 @@
       <c r="Q48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R48" s="3">
+      <c r="R48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S48" s="3">
         <v>2358700</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T48" s="3">
+      <c r="T48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U48" s="3">
         <v>837900</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V48" s="3">
+      <c r="V48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W48" s="3">
         <v>821800</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X48" s="3">
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y48" s="3">
         <v>685600</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z48" s="3">
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA48" s="3">
         <v>699000</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3">
         <v>662000</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD48" s="3">
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE48" s="3">
         <v>734800</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF48" s="3">
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG48" s="3">
         <v>709000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>6527400</v>
+        <v>6546000</v>
       </c>
       <c r="E49" s="3">
-        <v>7537500</v>
+        <v>7559000</v>
       </c>
       <c r="F49" s="3">
-        <v>7908600</v>
+        <v>7931200</v>
       </c>
       <c r="G49" s="3">
-        <v>7366100</v>
+        <v>7387100</v>
       </c>
       <c r="H49" s="3">
-        <v>6989600</v>
-      </c>
-      <c r="I49" s="3">
-        <v>6989600</v>
+        <v>7009500</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>5</v>
@@ -4135,53 +4245,56 @@
       <c r="Q49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R49" s="3">
+      <c r="R49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S49" s="3">
         <v>7980500</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T49" s="3">
+      <c r="T49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U49" s="3">
         <v>8524700</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V49" s="3">
+      <c r="V49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W49" s="3">
         <v>8070800</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X49" s="3">
+      <c r="X49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y49" s="3">
         <v>7053200</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z49" s="3">
+      <c r="Z49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA49" s="3">
         <v>7112300</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB49" s="3">
+      <c r="AB49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC49" s="3">
         <v>6528900</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD49" s="3">
+      <c r="AD49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE49" s="3">
         <v>7231800</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF49" s="3">
+      <c r="AF49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG49" s="3">
         <v>6802200</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,28 +4480,31 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>291900</v>
+        <v>292700</v>
       </c>
       <c r="E52" s="3">
-        <v>243000</v>
+        <v>243700</v>
       </c>
       <c r="F52" s="3">
-        <v>353700</v>
+        <v>354700</v>
       </c>
       <c r="G52" s="3">
-        <v>390600</v>
+        <v>391700</v>
       </c>
       <c r="H52" s="3">
-        <v>212700</v>
-      </c>
-      <c r="I52" s="3">
-        <v>227900</v>
+        <v>213300</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
@@ -4411,53 +4530,56 @@
       <c r="Q52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R52" s="3">
+      <c r="R52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S52" s="3">
         <v>173900</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T52" s="3">
+      <c r="T52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U52" s="3">
         <v>153100</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V52" s="3">
+      <c r="V52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W52" s="3">
         <v>172300</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X52" s="3">
+      <c r="X52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y52" s="3">
         <v>139600</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z52" s="3">
+      <c r="Z52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA52" s="3">
         <v>259200</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC52" s="3">
         <v>233400</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD52" s="3">
+      <c r="AD52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE52" s="3">
         <v>390900</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF52" s="3">
+      <c r="AF52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG52" s="3">
         <v>372100</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,28 +4670,31 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>22561500</v>
+        <v>22626000</v>
       </c>
       <c r="E54" s="3">
-        <v>22319500</v>
+        <v>22383300</v>
       </c>
       <c r="F54" s="3">
-        <v>22698200</v>
+        <v>22763100</v>
       </c>
       <c r="G54" s="3">
-        <v>21323500</v>
+        <v>21384400</v>
       </c>
       <c r="H54" s="3">
-        <v>20605200</v>
-      </c>
-      <c r="I54" s="3">
-        <v>19590800</v>
+        <v>20664100</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>5</v>
@@ -4595,53 +4720,56 @@
       <c r="Q54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R54" s="3">
+      <c r="R54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S54" s="3">
         <v>22072800</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T54" s="3">
+      <c r="T54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U54" s="3">
         <v>21396900</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V54" s="3">
+      <c r="V54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W54" s="3">
         <v>21189500</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X54" s="3">
+      <c r="X54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y54" s="3">
         <v>16924100</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z54" s="3">
+      <c r="Z54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA54" s="3">
         <v>17579300</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB54" s="3">
+      <c r="AB54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC54" s="3">
         <v>16688500</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD54" s="3">
+      <c r="AD54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE54" s="3">
         <v>18790400</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF54" s="3">
+      <c r="AF54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG54" s="3">
         <v>16618800</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,28 +4837,29 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2714700</v>
+        <v>2722400</v>
       </c>
       <c r="E57" s="3">
-        <v>3003300</v>
+        <v>3011900</v>
       </c>
       <c r="F57" s="3">
-        <v>2937100</v>
+        <v>2945500</v>
       </c>
       <c r="G57" s="3">
-        <v>2545400</v>
+        <v>2552700</v>
       </c>
       <c r="H57" s="3">
-        <v>2363100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>2130900</v>
+        <v>2369900</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
@@ -4755,73 +4885,76 @@
       <c r="Q57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R57" s="3">
+      <c r="R57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S57" s="3">
         <v>5469400</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T57" s="3">
+      <c r="T57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U57" s="3">
         <v>5992700</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V57" s="3">
+      <c r="V57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W57" s="3">
         <v>5415200</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X57" s="3">
+      <c r="X57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y57" s="3">
         <v>4676300</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z57" s="3">
+      <c r="Z57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA57" s="3">
         <v>4558600</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC57" s="3">
         <v>4435200</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD57" s="3">
+      <c r="AD57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE57" s="3">
         <v>4918300</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG57" s="3">
         <v>4630700</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>743200</v>
+        <v>745300</v>
       </c>
       <c r="E58" s="3">
-        <v>811600</v>
+        <v>813900</v>
       </c>
       <c r="F58" s="3">
-        <v>246300</v>
+        <v>247000</v>
       </c>
       <c r="G58" s="3">
-        <v>259300</v>
+        <v>260100</v>
       </c>
       <c r="H58" s="3">
-        <v>887500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>951500</v>
+        <v>890100</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>5</v>
@@ -4847,73 +4980,76 @@
       <c r="Q58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R58" s="3">
+      <c r="R58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S58" s="3">
         <v>1200200</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U58" s="3">
         <v>265800</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W58" s="3">
         <v>1506000</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X58" s="3">
+      <c r="X58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y58" s="3">
         <v>496200</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z58" s="3">
+      <c r="Z58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA58" s="3">
         <v>1318300</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB58" s="3">
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC58" s="3">
         <v>601400</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD58" s="3">
+      <c r="AD58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE58" s="3">
         <v>845100</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF58" s="3">
+      <c r="AF58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG58" s="3">
         <v>83300</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7175100</v>
+        <v>7195600</v>
       </c>
       <c r="E59" s="3">
-        <v>6855000</v>
+        <v>6874600</v>
       </c>
       <c r="F59" s="3">
-        <v>6876700</v>
+        <v>6896400</v>
       </c>
       <c r="G59" s="3">
-        <v>6850700</v>
+        <v>6870300</v>
       </c>
       <c r="H59" s="3">
-        <v>6354800</v>
-      </c>
-      <c r="I59" s="3">
-        <v>6558800</v>
+        <v>6373000</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>5</v>
@@ -4939,73 +5075,76 @@
       <c r="Q59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R59" s="3">
+      <c r="R59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S59" s="3">
         <v>3881800</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T59" s="3">
+      <c r="T59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U59" s="3">
         <v>3844000</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V59" s="3">
+      <c r="V59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W59" s="3">
         <v>3910400</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X59" s="3">
+      <c r="X59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y59" s="3">
         <v>3269600</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z59" s="3">
+      <c r="Z59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA59" s="3">
         <v>3474800</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB59" s="3">
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC59" s="3">
         <v>3287400</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD59" s="3">
+      <c r="AD59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE59" s="3">
         <v>3824300</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AF59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG59" s="3">
         <v>3393500</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>10633000</v>
+        <v>10663400</v>
       </c>
       <c r="E60" s="3">
-        <v>10669900</v>
+        <v>10700400</v>
       </c>
       <c r="F60" s="3">
-        <v>10060100</v>
+        <v>10088900</v>
       </c>
       <c r="G60" s="3">
-        <v>9655400</v>
+        <v>9683000</v>
       </c>
       <c r="H60" s="3">
-        <v>9605500</v>
-      </c>
-      <c r="I60" s="3">
-        <v>9641300</v>
+        <v>9632900</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>5</v>
@@ -5031,73 +5170,76 @@
       <c r="Q60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R60" s="3">
+      <c r="R60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S60" s="3">
         <v>10551400</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T60" s="3">
+      <c r="T60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U60" s="3">
         <v>10102500</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V60" s="3">
+      <c r="V60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W60" s="3">
         <v>10831600</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X60" s="3">
+      <c r="X60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y60" s="3">
         <v>8442100</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z60" s="3">
+      <c r="Z60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA60" s="3">
         <v>9351800</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB60" s="3">
+      <c r="AB60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC60" s="3">
         <v>8324000</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD60" s="3">
+      <c r="AD60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE60" s="3">
         <v>9587700</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF60" s="3">
+      <c r="AF60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG60" s="3">
         <v>8107500</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6226800</v>
+        <v>6244600</v>
       </c>
       <c r="E61" s="3">
-        <v>6344000</v>
+        <v>6362100</v>
       </c>
       <c r="F61" s="3">
-        <v>7015600</v>
+        <v>7035700</v>
       </c>
       <c r="G61" s="3">
-        <v>6873500</v>
+        <v>6893100</v>
       </c>
       <c r="H61" s="3">
-        <v>6743300</v>
+        <v>6762500</v>
       </c>
       <c r="I61" s="3">
-        <v>5875300</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -5124,72 +5266,75 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>5750500</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>4779900</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>4275200</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>3917600</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>3340200</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>3378300</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>3613000</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>2952100</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>760600</v>
+        <v>762800</v>
       </c>
       <c r="E62" s="3">
-        <v>857200</v>
+        <v>859600</v>
       </c>
       <c r="F62" s="3">
-        <v>821300</v>
+        <v>823700</v>
       </c>
       <c r="G62" s="3">
-        <v>861500</v>
+        <v>864000</v>
       </c>
       <c r="H62" s="3">
-        <v>811600</v>
-      </c>
-      <c r="I62" s="3">
-        <v>893000</v>
+        <v>813900</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>5</v>
@@ -5215,53 +5360,56 @@
       <c r="Q62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R62" s="3">
+      <c r="R62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S62" s="3">
         <v>1089600</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T62" s="3">
+      <c r="T62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U62" s="3">
         <v>1004500</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V62" s="3">
+      <c r="V62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W62" s="3">
         <v>1245200</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X62" s="3">
+      <c r="X62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y62" s="3">
         <v>878300</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="Z62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA62" s="3">
         <v>1098400</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB62" s="3">
+      <c r="AB62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC62" s="3">
         <v>980600</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD62" s="3">
+      <c r="AD62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE62" s="3">
         <v>1348700</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AF62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG62" s="3">
         <v>1213700</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,28 +5690,31 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>17633400</v>
+        <v>17683800</v>
       </c>
       <c r="E66" s="3">
-        <v>17875400</v>
+        <v>17926400</v>
       </c>
       <c r="F66" s="3">
-        <v>17907900</v>
+        <v>17959100</v>
       </c>
       <c r="G66" s="3">
-        <v>17401200</v>
+        <v>17450900</v>
       </c>
       <c r="H66" s="3">
-        <v>17168000</v>
-      </c>
-      <c r="I66" s="3">
-        <v>16425800</v>
+        <v>17217000</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>5</v>
@@ -5583,53 +5740,56 @@
       <c r="Q66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R66" s="3">
+      <c r="R66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S66" s="3">
         <v>17445700</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T66" s="3">
+      <c r="T66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U66" s="3">
         <v>15938300</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V66" s="3">
+      <c r="V66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W66" s="3">
         <v>16407100</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X66" s="3">
+      <c r="X66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y66" s="3">
         <v>13287900</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z66" s="3">
+      <c r="Z66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA66" s="3">
         <v>13828500</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB66" s="3">
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="3">
         <v>12721100</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD66" s="3">
+      <c r="AD66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE66" s="3">
         <v>14595200</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF66" s="3">
+      <c r="AF66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG66" s="3">
         <v>12313300</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,28 +6200,31 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4898800</v>
+        <v>4912800</v>
       </c>
       <c r="E72" s="3">
-        <v>4401800</v>
+        <v>4414400</v>
       </c>
       <c r="F72" s="3">
-        <v>4331300</v>
+        <v>4343700</v>
       </c>
       <c r="G72" s="3">
-        <v>3979800</v>
+        <v>3991200</v>
       </c>
       <c r="H72" s="3">
-        <v>3748700</v>
-      </c>
-      <c r="I72" s="3">
-        <v>3626100</v>
+        <v>3759400</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>5</v>
@@ -6077,53 +6250,56 @@
       <c r="Q72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S72" s="3">
         <v>4546900</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U72" s="3">
         <v>5338500</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W72" s="3">
         <v>5132900</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y72" s="3">
         <v>4203300</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA72" s="3">
         <v>3846200</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3">
         <v>3876500</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE72" s="3">
         <v>3539000</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG72" s="3">
         <v>3530800</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,28 +6580,31 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4928100</v>
+        <v>4942200</v>
       </c>
       <c r="E76" s="3">
-        <v>4444200</v>
+        <v>4456900</v>
       </c>
       <c r="F76" s="3">
-        <v>4790300</v>
+        <v>4804000</v>
       </c>
       <c r="G76" s="3">
-        <v>3922300</v>
+        <v>3933500</v>
       </c>
       <c r="H76" s="3">
-        <v>3437300</v>
-      </c>
-      <c r="I76" s="3">
-        <v>3164900</v>
+        <v>3447100</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>5</v>
@@ -6445,53 +6630,56 @@
       <c r="Q76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R76" s="3">
+      <c r="R76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S76" s="3">
         <v>4627100</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T76" s="3">
+      <c r="T76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U76" s="3">
         <v>5458600</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V76" s="3">
+      <c r="V76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W76" s="3">
         <v>4782400</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X76" s="3">
+      <c r="X76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y76" s="3">
         <v>3636300</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z76" s="3">
+      <c r="Z76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA76" s="3">
         <v>3750800</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB76" s="3">
+      <c r="AB76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC76" s="3">
         <v>3967400</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD76" s="3">
+      <c r="AD76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE76" s="3">
         <v>4195200</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF76" s="3">
+      <c r="AF76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG76" s="3">
         <v>4305500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E80" s="2">
         <v>45169</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45077</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44985</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44895</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44804</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44712</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44620</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44530</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44439</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44347</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44255</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44165</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44074</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43982</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43890</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43799</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43708</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43616</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43524</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43434</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43343</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43251</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43159</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43069</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42978</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42886</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42794</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42704</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>384100</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F81" s="3">
-        <v>477400</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H81" s="3">
-        <v>388400</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="3">
+        <v>385200</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3">
+        <v>478800</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I81" s="3">
+        <v>389500</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K81" s="3">
         <v>365600</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M81" s="3">
         <v>114200</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O81" s="3">
         <v>33700</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-719300</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S81" s="3">
         <v>426800</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="T81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U81" s="3">
         <v>368700</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W81" s="3">
         <v>435400</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="X81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y81" s="3">
         <v>309000</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="Z81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA81" s="3">
         <v>417400</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB81" s="3">
+      <c r="AB81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC81" s="3">
         <v>420700</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD81" s="3">
+      <c r="AD81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE81" s="3">
         <v>408500</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF81" s="3">
+      <c r="AF81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG81" s="3">
         <v>326300</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
+        <v>498300</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
+        <v>286200</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L83" s="3">
+        <v>569100</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M83" s="3">
         <v>647200</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3">
         <v>930000</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U83" s="3">
         <v>219300</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V83" s="3">
+      <c r="V83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W83" s="3">
         <v>222500</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y83" s="3">
         <v>178300</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA83" s="3">
         <v>175000</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="AB83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC83" s="3">
         <v>158200</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AD83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE83" s="3">
         <v>164300</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AF83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG83" s="3">
         <v>154900</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
+        <v>1497200</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
+        <v>324300</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L89" s="3">
+        <v>1126200</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3">
         <v>1056400</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="3">
         <v>653900</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U89" s="3">
         <v>1216400</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="V89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W89" s="3">
         <v>329000</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y89" s="3">
         <v>1061100</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="Z89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA89" s="3">
         <v>196300</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="AB89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC89" s="3">
         <v>1082700</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AD89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE89" s="3">
         <v>113900</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AF89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG89" s="3">
         <v>788800</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7702,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7507,76 +7727,79 @@
         <v>-137000</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-162000</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-236000</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="N91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-413100</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U91" s="3">
         <v>-241300</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="V91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W91" s="3">
         <v>-242800</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-200500</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-166100</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-185100</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AD91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-169000</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-201900</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
+        <v>-572300</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
+        <v>-303600</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L94" s="3">
+        <v>-420000</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M94" s="3">
         <v>-326300</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-446300</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U94" s="3">
         <v>-439800</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="V94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W94" s="3">
         <v>-538300</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-199400</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-920000</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AB94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-366900</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AD94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-334500</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AF94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-274700</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7894,19 +8127,19 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-383000</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-383000</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>-319900</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -7927,11 +8160,11 @@
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-441100</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -7945,11 +8178,11 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-482100</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -7957,11 +8190,11 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-461100</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
@@ -7969,16 +8202,19 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-421400</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
+        <v>-702900</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
+        <v>-569100</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3">
+        <v>-1206700</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3">
         <v>849700</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
         <v>205500</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U100" s="3">
         <v>-920000</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="V100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W100" s="3">
         <v>410300</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-519500</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA100" s="3">
         <v>139100</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AB100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-157100</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AD100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE100" s="3">
         <v>542300</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AF100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-332200</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
+        <v>-207800</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
+        <v>-108800</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3">
+        <v>157800</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3">
         <v>47400</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-127700</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U101" s="3">
         <v>-17100</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="V101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W101" s="3">
         <v>86100</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="X101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-120700</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="Z101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-23600</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB101" s="3">
+      <c r="AB101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-202000</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD101" s="3">
+      <c r="AD101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE101" s="3">
         <v>48100</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF101" s="3">
+      <c r="AF101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG101" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
+        <v>14100</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
+        <v>-657200</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L102" s="3">
+        <v>-342800</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M102" s="3">
         <v>1627200</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="3">
         <v>285400</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U102" s="3">
         <v>-160500</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="V102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W102" s="3">
         <v>287100</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y102" s="3">
         <v>221500</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="Z102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-608100</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AB102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC102" s="3">
         <v>356800</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AD102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE102" s="3">
         <v>369800</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AF102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG102" s="3">
         <v>186600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SDXAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SDXAY_QTR_FIN.xlsx
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45350</v>
+      </c>
+      <c r="E7" s="2">
         <v>45260</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45169</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45077</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44985</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44895</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44804</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44712</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44620</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44530</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44439</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44347</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44255</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44165</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44074</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43982</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43890</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43799</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43708</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43616</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43524</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43434</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43343</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43251</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43159</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43069</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42978</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42886</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42794</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42704</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6840900</v>
+        <v>13077600</v>
       </c>
       <c r="E8" s="3">
-        <v>11481600</v>
+        <v>6794400</v>
       </c>
       <c r="F8" s="3">
-        <v>6556900</v>
+        <v>11403500</v>
       </c>
       <c r="G8" s="3">
-        <v>13149700</v>
+        <v>6512300</v>
       </c>
       <c r="H8" s="3">
-        <v>6887700</v>
+        <v>12515600</v>
       </c>
       <c r="I8" s="3">
-        <v>10882100</v>
+        <v>6840800</v>
       </c>
       <c r="J8" s="3">
+        <v>10808100</v>
+      </c>
+      <c r="K8" s="3">
         <v>6009600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11134300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5706700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9512300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4744100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8773800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4420500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7918100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4266500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>13201400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7093200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>13363400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6684300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>13212000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6708200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11202300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5748000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11548600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5960000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11291700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6002600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>12482300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6398400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>11326100</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3">
-        <v>10436000</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3">
-        <v>11235700</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3">
-        <v>9809200</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="D9" s="3">
+        <v>11483500</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3">
+        <v>10365000</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="3">
+        <v>10988600</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="3">
+        <v>9742500</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" s="3">
         <v>9539300</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3">
         <v>8174700</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3">
         <v>7569200</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>7138700</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>11250400</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>11440200</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="3">
         <v>11264600</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="3">
         <v>9540900</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA9" s="3">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB9" s="3">
         <v>9768000</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC9" s="3">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="3">
         <v>9561600</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE9" s="3">
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="3">
         <v>10484500</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG9" s="3">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH9" s="3">
         <v>9595900</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1045700</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1914000</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1072900</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="D10" s="3">
+        <v>1594000</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1038600</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1527000</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1065600</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L10" s="3">
         <v>1595000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="3">
         <v>1337500</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3">
         <v>1204500</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
         <v>779500</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>1951100</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>1923200</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3">
         <v>1947400</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="3">
         <v>1661400</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB10" s="3">
         <v>1780600</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC10" s="3">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="3">
         <v>1730100</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE10" s="3">
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="3">
         <v>1997800</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG10" s="3">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH10" s="3">
         <v>1730200</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,76 +1318,79 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3">
-        <v>44600</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3">
-        <v>9800</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-58800</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="D14" s="3">
+        <v>-72400</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
+        <v>44300</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
+        <v>7600</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-58400</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>6500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>88300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>110200</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>438000</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>41800</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>41600</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>27500</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>5</v>
@@ -1381,89 +1401,92 @@
       <c r="AB14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF14" s="3">
         <v>12900</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="3">
-        <v>15200</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" s="3">
-        <v>23900</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I15" s="3">
-        <v>17400</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="D15" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3">
+        <v>15100</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="3">
+        <v>19500</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="3">
+        <v>17300</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L15" s="3">
         <v>21700</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N15" s="3">
         <v>12900</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P15" s="3">
         <v>21400</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="3">
         <v>4200</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T15" s="3">
         <v>22600</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V15" s="3">
         <v>51400</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X15" s="3">
         <v>51400</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
-      </c>
       <c r="Y15" s="3">
         <v>0</v>
       </c>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E17" s="3">
-        <v>11280300</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" s="3">
-        <v>12429400</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I17" s="3">
-        <v>10582900</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="D17" s="3">
+        <v>12383700</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3">
+        <v>11203600</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3">
+        <v>11965500</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3">
+        <v>10510900</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="3">
         <v>10551600</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N17" s="3">
         <v>9293600</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="3">
         <v>8634900</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3">
         <v>8493100</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="3">
         <v>12502500</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17" s="3">
         <v>12774200</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="3">
         <v>12520600</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="3">
         <v>10711600</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB17" s="3">
         <v>10927100</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="3">
         <v>10615100</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE17" s="3">
+      <c r="AE17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF17" s="3">
         <v>11807400</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG17" s="3">
+      <c r="AG17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH17" s="3">
         <v>10769700</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18" s="3">
-        <v>201300</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="3">
-        <v>720300</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I18" s="3">
-        <v>299200</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="D18" s="3">
+        <v>693800</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3">
+        <v>199900</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3">
+        <v>550100</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3">
+        <v>297200</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L18" s="3">
         <v>582600</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N18" s="3">
         <v>218600</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="3">
         <v>138800</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3">
         <v>-575000</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>698900</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="3">
         <v>589200</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="3">
         <v>691400</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="3">
         <v>490700</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB18" s="3">
         <v>621600</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="3">
         <v>676600</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF18" s="3">
         <v>674900</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH18" s="3">
         <v>556400</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,126 +1781,130 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="3">
-        <v>32600</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="3">
-        <v>33700</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="3">
-        <v>25000</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="D20" s="3">
+        <v>46500</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
+        <v>32400</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3">
+        <v>35700</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3">
+        <v>24900</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-1100</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>3200</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>4100</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-153600</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>9000</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="3">
         <v>22000</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" s="3">
         <v>8400</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z20" s="3">
         <v>12200</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="3">
         <v>12300</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF20" s="3">
         <v>5900</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3">
-        <v>732300</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1040200</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="3">
-        <v>893300</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>994200</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="3">
+        <v>727300</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" s="3">
+        <v>832100</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J21" s="3">
+        <v>887300</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1875,356 +1912,368 @@
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="3">
         <v>869100</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>201400</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>830500</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>922300</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>681200</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3">
         <v>809000</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>833600</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF21" s="3">
         <v>845100</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH21" s="3">
         <v>699600</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="3">
-        <v>87000</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G22" s="3">
-        <v>86000</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I22" s="3">
-        <v>60900</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="D22" s="3">
+        <v>92900</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3">
+        <v>86500</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3">
+        <v>82100</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3">
+        <v>60500</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3">
         <v>56400</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="3">
         <v>61400</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="3">
         <v>53100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="3">
         <v>77800</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="3">
         <v>80200</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V22" s="3">
         <v>75900</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="3">
         <v>70600</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="3">
         <v>62000</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB22" s="3">
         <v>60600</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD22" s="3">
         <v>51600</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF22" s="3">
         <v>56300</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG22" s="3">
+      <c r="AG22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH22" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="3">
-        <v>146900</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G23" s="3">
-        <v>668100</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I23" s="3">
-        <v>263300</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="D23" s="3">
+        <v>647300</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3">
+        <v>145900</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="3">
+        <v>503600</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3">
+        <v>261500</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="3">
         <v>525100</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="3">
         <v>160500</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P23" s="3">
         <v>89800</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3">
         <v>-806400</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="3">
         <v>627800</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V23" s="3">
         <v>535300</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X23" s="3">
         <v>629200</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="3">
         <v>440800</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA23" s="3">
+      <c r="AA23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB23" s="3">
         <v>573300</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC23" s="3">
+      <c r="AC23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD23" s="3">
         <v>623800</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE23" s="3">
+      <c r="AE23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF23" s="3">
         <v>624500</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG23" s="3">
+      <c r="AG23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH23" s="3">
         <v>486000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="3">
-        <v>16300</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="D24" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3">
+        <v>16200</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3">
+        <v>131800</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3">
+        <v>75600</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L24" s="3">
+        <v>147600</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N24" s="3">
+        <v>51700</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P24" s="3">
+        <v>54100</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3">
+        <v>-65400</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="3">
+        <v>181800</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="3">
+        <v>154300</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X24" s="3">
         <v>180600</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I24" s="3">
-        <v>76200</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K24" s="3">
-        <v>147600</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M24" s="3">
-        <v>51700</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O24" s="3">
-        <v>54100</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>-65400</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S24" s="3">
-        <v>181800</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U24" s="3">
-        <v>154300</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W24" s="3">
-        <v>180600</v>
-      </c>
-      <c r="X24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z24" s="3">
         <v>126300</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA24" s="3">
+      <c r="AA24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB24" s="3">
         <v>147000</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC24" s="3">
+      <c r="AC24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD24" s="3">
         <v>191900</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE24" s="3">
+      <c r="AE24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF24" s="3">
         <v>201900</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG24" s="3">
+      <c r="AG24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH24" s="3">
         <v>150200</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26" s="3">
-        <v>130600</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G26" s="3">
-        <v>487500</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I26" s="3">
-        <v>187200</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="D26" s="3">
+        <v>540400</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3">
+        <v>129700</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3">
+        <v>371800</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="3">
+        <v>185900</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L26" s="3">
         <v>377600</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N26" s="3">
         <v>108800</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="3">
         <v>35700</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3">
         <v>-741100</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="3">
         <v>446000</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V26" s="3">
         <v>381000</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X26" s="3">
         <v>448600</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z26" s="3">
         <v>314600</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB26" s="3">
         <v>426400</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC26" s="3">
+      <c r="AC26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD26" s="3">
         <v>432000</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE26" s="3">
+      <c r="AE26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF26" s="3">
         <v>422600</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG26" s="3">
+      <c r="AG26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH26" s="3">
         <v>335700</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="3">
-        <v>130600</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G27" s="3">
-        <v>478800</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I27" s="3">
-        <v>192600</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="D27" s="3">
+        <v>536000</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3">
+        <v>129700</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3">
+        <v>366400</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="3">
+        <v>191300</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L27" s="3">
         <v>365600</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N27" s="3">
         <v>114200</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="3">
         <v>33700</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3">
         <v>-719300</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
         <v>426800</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V27" s="3">
         <v>368700</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X27" s="3">
         <v>435400</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z27" s="3">
         <v>309000</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB27" s="3">
         <v>417400</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC27" s="3">
+      <c r="AC27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD27" s="3">
         <v>420700</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE27" s="3">
+      <c r="AE27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF27" s="3">
         <v>408500</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG27" s="3">
+      <c r="AG27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH27" s="3">
         <v>326300</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,37 +2661,40 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3">
-        <v>254600</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>5</v>
+      <c r="D29" s="3">
+        <v>-616000</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="3">
+        <v>252900</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I29" s="3">
-        <v>196900</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>5</v>
+      <c r="H29" s="3">
+        <v>109200</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J29" s="3">
+        <v>195600</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-32600</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-33700</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-25000</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="D32" s="3">
+        <v>-46500</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-35700</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>1100</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>-3200</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>-4100</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>153600</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>-9000</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3">
         <v>-22000</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X32" s="3">
         <v>-8400</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-12300</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD32" s="3">
         <v>1100</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-5900</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH32" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33" s="3">
-        <v>385200</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G33" s="3">
-        <v>478800</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I33" s="3">
-        <v>389500</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="D33" s="3">
+        <v>-80000</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3">
+        <v>382600</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3">
+        <v>475500</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="3">
+        <v>386900</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L33" s="3">
         <v>365600</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N33" s="3">
         <v>114200</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P33" s="3">
         <v>33700</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3">
         <v>-719300</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3">
         <v>426800</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3">
         <v>368700</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" s="3">
         <v>435400</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z33" s="3">
         <v>309000</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB33" s="3">
         <v>417400</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC33" s="3">
+      <c r="AC33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD33" s="3">
         <v>420700</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE33" s="3">
+      <c r="AE33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF33" s="3">
         <v>408500</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG33" s="3">
+      <c r="AG33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH33" s="3">
         <v>326300</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E35" s="3">
-        <v>385200</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G35" s="3">
-        <v>478800</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I35" s="3">
-        <v>389500</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="D35" s="3">
+        <v>-80000</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3">
+        <v>382600</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="3">
+        <v>475500</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="3">
+        <v>386900</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" s="3">
         <v>365600</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N35" s="3">
         <v>114200</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P35" s="3">
         <v>33700</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3">
         <v>-719300</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="3">
         <v>426800</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V35" s="3">
         <v>368700</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3">
         <v>435400</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z35" s="3">
         <v>309000</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB35" s="3">
         <v>417400</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC35" s="3">
+      <c r="AC35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD35" s="3">
         <v>420700</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE35" s="3">
+      <c r="AE35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF35" s="3">
         <v>408500</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG35" s="3">
+      <c r="AG35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH35" s="3">
         <v>326300</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45350</v>
+      </c>
+      <c r="E38" s="2">
         <v>45260</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45169</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45077</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44985</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44895</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44804</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44712</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44620</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44530</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44439</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44347</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44255</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44165</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44074</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43982</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43890</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43799</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43708</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43616</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43524</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43434</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43343</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43251</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43159</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43069</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42978</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42886</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42794</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42704</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,28 +3524,29 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2166400</v>
+        <v>1527000</v>
       </c>
       <c r="E41" s="3">
-        <v>2225200</v>
+        <v>2151700</v>
       </c>
       <c r="F41" s="3">
-        <v>2939000</v>
+        <v>2210000</v>
       </c>
       <c r="G41" s="3">
-        <v>2361200</v>
+        <v>2919000</v>
       </c>
       <c r="H41" s="3">
-        <v>3492800</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>5</v>
+        <v>2345100</v>
+      </c>
+      <c r="I41" s="3">
+        <v>3469000</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>5</v>
@@ -3488,73 +3575,76 @@
       <c r="R41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S41" s="3">
+      <c r="S41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T41" s="3">
         <v>1505100</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V41" s="3">
         <v>1723600</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W41" s="3">
+      <c r="W41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X41" s="3">
         <v>1824200</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y41" s="3">
+      <c r="Y41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z41" s="3">
         <v>1441000</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA41" s="3">
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB41" s="3">
         <v>1216200</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC41" s="3">
+      <c r="AC41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD41" s="3">
         <v>1792900</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE41" s="3">
+      <c r="AE41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF41" s="3">
         <v>1472000</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG41" s="3">
+      <c r="AG41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH41" s="3">
         <v>1199600</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>117500</v>
+        <v>129700</v>
       </c>
       <c r="E42" s="3">
-        <v>698600</v>
+        <v>116700</v>
       </c>
       <c r="F42" s="3">
-        <v>632200</v>
+        <v>693800</v>
       </c>
       <c r="G42" s="3">
-        <v>532100</v>
+        <v>627900</v>
       </c>
       <c r="H42" s="3">
-        <v>400400</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>5</v>
+        <v>528500</v>
+      </c>
+      <c r="I42" s="3">
+        <v>397700</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>5</v>
@@ -3583,73 +3673,76 @@
       <c r="R42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S42" s="3">
+      <c r="S42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T42" s="3">
         <v>465200</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U42" s="3">
+      <c r="U42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V42" s="3">
         <v>529200</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W42" s="3">
+      <c r="W42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X42" s="3">
         <v>553800</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y42" s="3">
+      <c r="Y42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z42" s="3">
         <v>444100</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA42" s="3">
+      <c r="AA42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB42" s="3">
         <v>526200</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC42" s="3">
+      <c r="AC42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD42" s="3">
         <v>507100</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE42" s="3">
+      <c r="AE42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF42" s="3">
         <v>563400</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG42" s="3">
+      <c r="AG42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH42" s="3">
         <v>466000</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3967200</v>
+        <v>4616800</v>
       </c>
       <c r="E43" s="3">
-        <v>6337100</v>
+        <v>3940200</v>
       </c>
       <c r="F43" s="3">
-        <v>5700600</v>
+        <v>6294000</v>
       </c>
       <c r="G43" s="3">
-        <v>5762600</v>
+        <v>5661800</v>
       </c>
       <c r="H43" s="3">
-        <v>4819200</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>5</v>
+        <v>5723400</v>
+      </c>
+      <c r="I43" s="3">
+        <v>4786400</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>5</v>
@@ -3678,168 +3771,174 @@
       <c r="R43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S43" s="3">
+      <c r="S43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T43" s="3">
         <v>6273300</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U43" s="3">
+      <c r="U43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V43" s="3">
         <v>5819900</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W43" s="3">
+      <c r="W43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X43" s="3">
         <v>6270500</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y43" s="3">
+      <c r="Y43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z43" s="3">
         <v>4759400</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA43" s="3">
+      <c r="AA43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB43" s="3">
         <v>5479800</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC43" s="3">
+      <c r="AC43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD43" s="3">
         <v>4751600</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE43" s="3">
+      <c r="AE43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF43" s="3">
         <v>6121400</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG43" s="3">
+      <c r="AG43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH43" s="3">
         <v>4899500</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>352500</v>
+        <v>346900</v>
       </c>
       <c r="E44" s="3">
-        <v>380800</v>
+        <v>350100</v>
       </c>
       <c r="F44" s="3">
-        <v>383000</v>
+        <v>378200</v>
       </c>
       <c r="G44" s="3">
+        <v>380400</v>
+      </c>
+      <c r="H44" s="3">
+        <v>325300</v>
+      </c>
+      <c r="I44" s="3">
+        <v>276700</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T44" s="3">
+        <v>337600</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V44" s="3">
+        <v>360100</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X44" s="3">
+        <v>346900</v>
+      </c>
+      <c r="Y44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>310100</v>
+      </c>
+      <c r="AA44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB44" s="3">
+        <v>314200</v>
+      </c>
+      <c r="AC44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD44" s="3">
+        <v>288400</v>
+      </c>
+      <c r="AE44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF44" s="3">
         <v>327500</v>
       </c>
-      <c r="H44" s="3">
-        <v>278600</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S44" s="3">
-        <v>337600</v>
-      </c>
-      <c r="T44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U44" s="3">
-        <v>360100</v>
-      </c>
-      <c r="V44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W44" s="3">
-        <v>346900</v>
-      </c>
-      <c r="X44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y44" s="3">
-        <v>310100</v>
-      </c>
-      <c r="Z44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA44" s="3">
-        <v>314200</v>
-      </c>
-      <c r="AB44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC44" s="3">
-        <v>288400</v>
-      </c>
-      <c r="AD44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE44" s="3">
-        <v>327500</v>
-      </c>
-      <c r="AF44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG44" s="3">
+      <c r="AG44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH44" s="3">
         <v>314600</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5787600</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>1408000</v>
+        <v>5748200</v>
       </c>
       <c r="F45" s="3">
-        <v>1373200</v>
+        <v>1398400</v>
       </c>
       <c r="G45" s="3">
-        <v>1451500</v>
+        <v>1363800</v>
       </c>
       <c r="H45" s="3">
-        <v>1489600</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
+        <v>1441700</v>
+      </c>
+      <c r="I45" s="3">
+        <v>1479500</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>5</v>
@@ -3868,73 +3967,76 @@
       <c r="R45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S45" s="3">
+      <c r="S45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T45" s="3">
         <v>1129100</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V45" s="3">
         <v>1381800</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W45" s="3">
+      <c r="W45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X45" s="3">
         <v>1252400</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y45" s="3">
+      <c r="Y45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z45" s="3">
         <v>1170700</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA45" s="3">
+      <c r="AA45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB45" s="3">
         <v>1088300</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AC45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD45" s="3">
         <v>1027700</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE45" s="3">
+      <c r="AE45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF45" s="3">
         <v>1014200</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG45" s="3">
+      <c r="AG45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH45" s="3">
         <v>937900</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>12391300</v>
+        <v>6620400</v>
       </c>
       <c r="E46" s="3">
-        <v>11049700</v>
+        <v>12307000</v>
       </c>
       <c r="F46" s="3">
-        <v>11027900</v>
+        <v>10974500</v>
       </c>
       <c r="G46" s="3">
-        <v>10434900</v>
+        <v>10952900</v>
       </c>
       <c r="H46" s="3">
-        <v>10480600</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>5</v>
+        <v>10363900</v>
+      </c>
+      <c r="I46" s="3">
+        <v>10409300</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>5</v>
@@ -3963,73 +4065,76 @@
       <c r="R46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S46" s="3">
+      <c r="S46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T46" s="3">
         <v>9710300</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U46" s="3">
+      <c r="U46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V46" s="3">
         <v>9814600</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W46" s="3">
+      <c r="W46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X46" s="3">
         <v>10247800</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y46" s="3">
+      <c r="Y46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z46" s="3">
         <v>8125400</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA46" s="3">
+      <c r="AA46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB46" s="3">
         <v>8624700</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC46" s="3">
+      <c r="AC46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD46" s="3">
         <v>8367800</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE46" s="3">
+      <c r="AE46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF46" s="3">
         <v>9498500</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG46" s="3">
+      <c r="AG46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH46" s="3">
         <v>7817600</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1984700</v>
+        <v>2025200</v>
       </c>
       <c r="E47" s="3">
-        <v>2058700</v>
+        <v>1971200</v>
       </c>
       <c r="F47" s="3">
-        <v>1920500</v>
+        <v>2044700</v>
       </c>
       <c r="G47" s="3">
-        <v>1675700</v>
+        <v>1907400</v>
       </c>
       <c r="H47" s="3">
-        <v>1476600</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
+        <v>1664300</v>
+      </c>
+      <c r="I47" s="3">
+        <v>1466500</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>5</v>
@@ -4058,73 +4163,76 @@
       <c r="R47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T47" s="3">
         <v>1849500</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V47" s="3">
         <v>2066600</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X47" s="3">
         <v>1876800</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z47" s="3">
         <v>920400</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB47" s="3">
         <v>884100</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD47" s="3">
         <v>896500</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF47" s="3">
         <v>934400</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG47" s="3">
+      <c r="AG47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH47" s="3">
         <v>917900</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1411300</v>
+        <v>1366000</v>
       </c>
       <c r="E48" s="3">
-        <v>1472200</v>
+        <v>1401700</v>
       </c>
       <c r="F48" s="3">
-        <v>1528800</v>
+        <v>1462200</v>
       </c>
       <c r="G48" s="3">
-        <v>1495000</v>
+        <v>1518400</v>
       </c>
       <c r="H48" s="3">
-        <v>1484200</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
+        <v>1484900</v>
+      </c>
+      <c r="I48" s="3">
+        <v>1474100</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
@@ -4153,73 +4261,76 @@
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S48" s="3">
+      <c r="S48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T48" s="3">
         <v>2358700</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3">
         <v>837900</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X48" s="3">
         <v>821800</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3">
         <v>685600</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3">
         <v>699000</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3">
         <v>662000</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF48" s="3">
         <v>734800</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH48" s="3">
         <v>709000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>6546000</v>
+        <v>6529600</v>
       </c>
       <c r="E49" s="3">
-        <v>7559000</v>
+        <v>6501500</v>
       </c>
       <c r="F49" s="3">
-        <v>7931200</v>
+        <v>7507600</v>
       </c>
       <c r="G49" s="3">
-        <v>7387100</v>
+        <v>7877200</v>
       </c>
       <c r="H49" s="3">
-        <v>7009500</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>5</v>
+        <v>7336900</v>
+      </c>
+      <c r="I49" s="3">
+        <v>6961900</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>5</v>
@@ -4248,53 +4359,56 @@
       <c r="R49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S49" s="3">
+      <c r="S49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T49" s="3">
         <v>7980500</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U49" s="3">
+      <c r="U49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V49" s="3">
         <v>8524700</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W49" s="3">
+      <c r="W49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X49" s="3">
         <v>8070800</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y49" s="3">
+      <c r="Y49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z49" s="3">
         <v>7053200</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB49" s="3">
         <v>7112300</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC49" s="3">
+      <c r="AC49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD49" s="3">
         <v>6528900</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF49" s="3">
         <v>7231800</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH49" s="3">
         <v>6802200</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,28 +4600,31 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>292700</v>
+        <v>313400</v>
       </c>
       <c r="E52" s="3">
-        <v>243700</v>
+        <v>290700</v>
       </c>
       <c r="F52" s="3">
-        <v>354700</v>
+        <v>242100</v>
       </c>
       <c r="G52" s="3">
-        <v>391700</v>
+        <v>352300</v>
       </c>
       <c r="H52" s="3">
-        <v>213300</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
+        <v>389100</v>
+      </c>
+      <c r="I52" s="3">
+        <v>211800</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
@@ -4533,53 +4653,56 @@
       <c r="R52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T52" s="3">
         <v>173900</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V52" s="3">
         <v>153100</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W52" s="3">
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X52" s="3">
         <v>172300</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z52" s="3">
         <v>139600</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB52" s="3">
         <v>259200</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
         <v>233400</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF52" s="3">
         <v>390900</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH52" s="3">
         <v>372100</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,28 +4796,31 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>22626000</v>
+        <v>16854600</v>
       </c>
       <c r="E54" s="3">
-        <v>22383300</v>
+        <v>22472100</v>
       </c>
       <c r="F54" s="3">
-        <v>22763100</v>
+        <v>22231100</v>
       </c>
       <c r="G54" s="3">
-        <v>21384400</v>
+        <v>22608200</v>
       </c>
       <c r="H54" s="3">
-        <v>20664100</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>5</v>
+        <v>21239000</v>
+      </c>
+      <c r="I54" s="3">
+        <v>20523600</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>5</v>
@@ -4723,53 +4849,56 @@
       <c r="R54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S54" s="3">
+      <c r="S54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T54" s="3">
         <v>22072800</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V54" s="3">
         <v>21396900</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W54" s="3">
+      <c r="W54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X54" s="3">
         <v>21189500</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y54" s="3">
+      <c r="Y54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z54" s="3">
         <v>16924100</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA54" s="3">
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB54" s="3">
         <v>17579300</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC54" s="3">
+      <c r="AC54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD54" s="3">
         <v>16688500</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE54" s="3">
+      <c r="AE54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF54" s="3">
         <v>18790400</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG54" s="3">
+      <c r="AG54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH54" s="3">
         <v>16618800</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,28 +4968,29 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2722400</v>
+        <v>2788200</v>
       </c>
       <c r="E57" s="3">
-        <v>3011900</v>
+        <v>2703900</v>
       </c>
       <c r="F57" s="3">
-        <v>2945500</v>
+        <v>2991400</v>
       </c>
       <c r="G57" s="3">
-        <v>2552700</v>
+        <v>2925500</v>
       </c>
       <c r="H57" s="3">
-        <v>2369900</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
+        <v>2535300</v>
+      </c>
+      <c r="I57" s="3">
+        <v>2353800</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
@@ -4888,73 +5019,76 @@
       <c r="R57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T57" s="3">
         <v>5469400</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V57" s="3">
         <v>5992700</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X57" s="3">
         <v>5415200</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3">
         <v>4676300</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="3">
         <v>4558600</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="3">
         <v>4435200</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="3">
         <v>4918300</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH57" s="3">
         <v>4630700</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>745300</v>
+        <v>225900</v>
       </c>
       <c r="E58" s="3">
-        <v>813900</v>
+        <v>740300</v>
       </c>
       <c r="F58" s="3">
-        <v>247000</v>
+        <v>808400</v>
       </c>
       <c r="G58" s="3">
-        <v>260100</v>
+        <v>245300</v>
       </c>
       <c r="H58" s="3">
-        <v>890100</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>5</v>
+        <v>258300</v>
+      </c>
+      <c r="I58" s="3">
+        <v>884000</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>5</v>
@@ -4983,73 +5117,76 @@
       <c r="R58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T58" s="3">
         <v>1200200</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V58" s="3">
         <v>265800</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X58" s="3">
         <v>1506000</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z58" s="3">
         <v>496200</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB58" s="3">
         <v>1318300</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC58" s="3">
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD58" s="3">
         <v>601400</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE58" s="3">
+      <c r="AE58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF58" s="3">
         <v>845100</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG58" s="3">
+      <c r="AG58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH58" s="3">
         <v>83300</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7195600</v>
+        <v>2397000</v>
       </c>
       <c r="E59" s="3">
-        <v>6874600</v>
+        <v>7146700</v>
       </c>
       <c r="F59" s="3">
-        <v>6896400</v>
+        <v>6827900</v>
       </c>
       <c r="G59" s="3">
-        <v>6870300</v>
+        <v>6849500</v>
       </c>
       <c r="H59" s="3">
-        <v>6373000</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>5</v>
+        <v>6823500</v>
+      </c>
+      <c r="I59" s="3">
+        <v>6329700</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>5</v>
@@ -5078,73 +5215,76 @@
       <c r="R59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T59" s="3">
         <v>3881800</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V59" s="3">
         <v>3844000</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X59" s="3">
         <v>3910400</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3">
         <v>3269600</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB59" s="3">
         <v>3474800</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>3287400</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF59" s="3">
         <v>3824300</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH59" s="3">
         <v>3393500</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>10663400</v>
+        <v>5411100</v>
       </c>
       <c r="E60" s="3">
-        <v>10700400</v>
+        <v>10590900</v>
       </c>
       <c r="F60" s="3">
-        <v>10088900</v>
+        <v>10627600</v>
       </c>
       <c r="G60" s="3">
-        <v>9683000</v>
+        <v>10020300</v>
       </c>
       <c r="H60" s="3">
-        <v>9632900</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>5</v>
+        <v>9617100</v>
+      </c>
+      <c r="I60" s="3">
+        <v>9567400</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>5</v>
@@ -5173,73 +5313,76 @@
       <c r="R60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S60" s="3">
+      <c r="S60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T60" s="3">
         <v>10551400</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U60" s="3">
+      <c r="U60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V60" s="3">
         <v>10102500</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W60" s="3">
+      <c r="W60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X60" s="3">
         <v>10831600</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y60" s="3">
+      <c r="Y60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z60" s="3">
         <v>8442100</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA60" s="3">
+      <c r="AA60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB60" s="3">
         <v>9351800</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC60" s="3">
+      <c r="AC60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD60" s="3">
         <v>8324000</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE60" s="3">
+      <c r="AE60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF60" s="3">
         <v>9587700</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG60" s="3">
+      <c r="AG60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH60" s="3">
         <v>8107500</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6244600</v>
+        <v>5806600</v>
       </c>
       <c r="E61" s="3">
-        <v>6362100</v>
+        <v>6202100</v>
       </c>
       <c r="F61" s="3">
-        <v>7035700</v>
+        <v>6318900</v>
       </c>
       <c r="G61" s="3">
-        <v>6893100</v>
+        <v>6987800</v>
       </c>
       <c r="H61" s="3">
-        <v>6762500</v>
+        <v>6846200</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>6716600</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -5269,72 +5412,75 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>5750500</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>4779900</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>4275200</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>3917600</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>3340200</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>3378300</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>3613000</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>2952100</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>762800</v>
+        <v>849400</v>
       </c>
       <c r="E62" s="3">
-        <v>859600</v>
+        <v>757600</v>
       </c>
       <c r="F62" s="3">
-        <v>823700</v>
+        <v>853800</v>
       </c>
       <c r="G62" s="3">
-        <v>864000</v>
+        <v>818100</v>
       </c>
       <c r="H62" s="3">
-        <v>813900</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>5</v>
+        <v>858100</v>
+      </c>
+      <c r="I62" s="3">
+        <v>808400</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>5</v>
@@ -5363,53 +5509,56 @@
       <c r="R62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S62" s="3">
+      <c r="S62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T62" s="3">
         <v>1089600</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V62" s="3">
         <v>1004500</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W62" s="3">
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X62" s="3">
         <v>1245200</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z62" s="3">
         <v>878300</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB62" s="3">
         <v>1098400</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD62" s="3">
         <v>980600</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF62" s="3">
         <v>1348700</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH62" s="3">
         <v>1213700</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,28 +5848,31 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>17683800</v>
+        <v>12085500</v>
       </c>
       <c r="E66" s="3">
-        <v>17926400</v>
+        <v>17563500</v>
       </c>
       <c r="F66" s="3">
-        <v>17959100</v>
+        <v>17804500</v>
       </c>
       <c r="G66" s="3">
-        <v>17450900</v>
+        <v>17837000</v>
       </c>
       <c r="H66" s="3">
-        <v>17217000</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>5</v>
+        <v>17332300</v>
+      </c>
+      <c r="I66" s="3">
+        <v>17099900</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>5</v>
@@ -5743,53 +5901,56 @@
       <c r="R66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S66" s="3">
+      <c r="S66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T66" s="3">
         <v>17445700</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V66" s="3">
         <v>15938300</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W66" s="3">
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X66" s="3">
         <v>16407100</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z66" s="3">
         <v>13287900</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA66" s="3">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB66" s="3">
         <v>13828500</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC66" s="3">
+      <c r="AC66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD66" s="3">
         <v>12721100</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF66" s="3">
         <v>14595200</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH66" s="3">
         <v>12313300</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,28 +6374,31 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4912800</v>
+        <v>4197400</v>
       </c>
       <c r="E72" s="3">
-        <v>4414400</v>
+        <v>4879400</v>
       </c>
       <c r="F72" s="3">
-        <v>4343700</v>
+        <v>4384400</v>
       </c>
       <c r="G72" s="3">
-        <v>3991200</v>
+        <v>4314200</v>
       </c>
       <c r="H72" s="3">
-        <v>3759400</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>5</v>
+        <v>3964000</v>
+      </c>
+      <c r="I72" s="3">
+        <v>3733800</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>5</v>
@@ -6253,53 +6427,56 @@
       <c r="R72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T72" s="3">
         <v>4546900</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V72" s="3">
         <v>5338500</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X72" s="3">
         <v>5132900</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z72" s="3">
         <v>4203300</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB72" s="3">
         <v>3846200</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD72" s="3">
         <v>3876500</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF72" s="3">
         <v>3539000</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH72" s="3">
         <v>3530800</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,28 +6766,31 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4942200</v>
+        <v>4769100</v>
       </c>
       <c r="E76" s="3">
-        <v>4456900</v>
+        <v>4908500</v>
       </c>
       <c r="F76" s="3">
-        <v>4804000</v>
+        <v>4426500</v>
       </c>
       <c r="G76" s="3">
-        <v>3933500</v>
+        <v>4771300</v>
       </c>
       <c r="H76" s="3">
-        <v>3447100</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>5</v>
+        <v>3906700</v>
+      </c>
+      <c r="I76" s="3">
+        <v>3423700</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>5</v>
@@ -6633,53 +6819,56 @@
       <c r="R76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S76" s="3">
+      <c r="S76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T76" s="3">
         <v>4627100</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U76" s="3">
+      <c r="U76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V76" s="3">
         <v>5458600</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W76" s="3">
+      <c r="W76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X76" s="3">
         <v>4782400</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y76" s="3">
+      <c r="Y76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z76" s="3">
         <v>3636300</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA76" s="3">
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB76" s="3">
         <v>3750800</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC76" s="3">
+      <c r="AC76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD76" s="3">
         <v>3967400</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE76" s="3">
+      <c r="AE76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF76" s="3">
         <v>4195200</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG76" s="3">
+      <c r="AG76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH76" s="3">
         <v>4305500</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45350</v>
+      </c>
+      <c r="E80" s="2">
         <v>45260</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45169</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45077</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44985</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44895</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44804</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44712</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44620</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44530</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44439</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44347</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44255</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44165</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44074</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43982</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43890</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43799</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43708</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43616</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43524</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43434</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43343</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43251</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43159</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43069</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42978</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42886</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42794</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42704</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E81" s="3">
-        <v>385200</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G81" s="3">
-        <v>478800</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I81" s="3">
-        <v>389500</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="D81" s="3">
+        <v>-80000</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3">
+        <v>382600</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H81" s="3">
+        <v>475500</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J81" s="3">
+        <v>386900</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L81" s="3">
         <v>365600</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N81" s="3">
         <v>114200</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P81" s="3">
         <v>33700</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3">
         <v>-719300</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T81" s="3">
         <v>426800</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V81" s="3">
         <v>368700</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X81" s="3">
         <v>435400</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z81" s="3">
         <v>309000</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB81" s="3">
         <v>417400</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC81" s="3">
+      <c r="AC81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD81" s="3">
         <v>420700</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE81" s="3">
+      <c r="AE81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF81" s="3">
         <v>408500</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG81" s="3">
+      <c r="AG81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH81" s="3">
         <v>326300</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E83" s="3">
-        <v>498300</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G83" s="3">
-        <v>286200</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I83" s="3">
-        <v>569100</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="D83" s="3">
+        <v>254000</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3">
+        <v>495000</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3">
+        <v>284200</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3">
+        <v>565200</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>647200</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>930000</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
         <v>219300</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
         <v>222500</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z83" s="3">
         <v>178300</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB83" s="3">
         <v>175000</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD83" s="3">
         <v>158200</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF83" s="3">
         <v>164300</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH83" s="3">
         <v>154900</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E89" s="3">
-        <v>1497200</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="3">
-        <v>324300</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I89" s="3">
-        <v>1126200</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="D89" s="3">
+        <v>343700</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3">
+        <v>1487000</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3">
+        <v>322000</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3">
+        <v>1118500</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
         <v>1056400</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
         <v>653900</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
         <v>1216400</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
         <v>329000</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
         <v>1061100</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB89" s="3">
         <v>196300</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD89" s="3">
         <v>1082700</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF89" s="3">
         <v>113900</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH89" s="3">
         <v>788800</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-123000</v>
+        <v>-181000</v>
       </c>
       <c r="E91" s="3">
-        <v>-215000</v>
+        <v>-176000</v>
       </c>
       <c r="F91" s="3">
+        <v>-162000</v>
+      </c>
+      <c r="G91" s="3">
         <v>-187000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-158000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-159000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-137000</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-162000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-236000</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R91" s="3">
         <v>-413100</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V91" s="3">
         <v>-241300</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X91" s="3">
         <v>-242800</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-200500</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-166100</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-185100</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-169000</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-201900</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-572300</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-303600</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-420000</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="D94" s="3">
+        <v>-1955000</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-568400</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-261500</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-417200</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
         <v>-326300</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>-446300</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
         <v>-439800</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
         <v>-538300</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-199400</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-920000</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-366900</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-334500</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-274700</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,31 +8351,32 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-492800</v>
       </c>
       <c r="E96" s="3">
-        <v>-383000</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-380400</v>
       </c>
       <c r="G96" s="3">
-        <v>-383000</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-380400</v>
       </c>
       <c r="I96" s="3">
-        <v>-319900</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-317700</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8163,11 +8397,11 @@
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-441100</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -8181,11 +8415,11 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-482100</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -8193,11 +8427,11 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-461100</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
@@ -8205,16 +8439,19 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-421400</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-702900</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-569100</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-1206700</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="D100" s="3">
+        <v>-333900</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-698100</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-565200</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-1198500</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
         <v>849700</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>205500</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
         <v>-920000</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
         <v>410300</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-519500</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB100" s="3">
         <v>139100</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-157100</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF100" s="3">
         <v>542300</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-332200</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-207800</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-108800</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I101" s="3">
-        <v>157800</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="D101" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-206400</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-108100</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3">
+        <v>156700</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
         <v>47400</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
         <v>-127700</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
         <v>-17100</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3">
         <v>86100</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-120700</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA101" s="3">
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-23600</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-202000</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF101" s="3">
         <v>48100</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AG101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH101" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E102" s="3">
-        <v>14100</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-657200</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-342800</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="D102" s="3">
+        <v>-1929000</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F102" s="3">
+        <v>14000</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-652700</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-340400</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3">
         <v>1627200</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
         <v>285400</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
         <v>-160500</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
         <v>287100</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
         <v>221500</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-608100</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD102" s="3">
         <v>356800</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF102" s="3">
         <v>369800</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH102" s="3">
         <v>186600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SDXAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SDXAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
   <si>
     <t>SDXAY</t>
   </si>
@@ -656,69 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45991</v>
+      </c>
+      <c r="F7" s="2">
         <v>45900</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45808</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45716</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45626</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45535</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45443</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45351</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45260</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45169</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45077</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -752,8 +759,14 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -787,8 +800,14 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,8 +841,14 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,8 +862,10 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -872,8 +899,14 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,8 +940,14 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -942,8 +981,14 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -977,8 +1022,14 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,8 +1040,10 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1024,8 +1077,14 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1059,8 +1118,14 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,8 +1139,10 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1109,8 +1176,14 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1144,8 +1217,14 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1179,8 +1258,14 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1214,8 +1299,14 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1249,8 +1340,14 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,8 +1381,14 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1319,8 +1422,14 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1354,8 +1463,14 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1504,14 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1545,14 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1586,14 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,8 +1627,14 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1529,8 +1668,14 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1564,8 +1709,14 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,8 +1750,14 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1634,48 +1791,60 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45991</v>
+      </c>
+      <c r="F38" s="2">
         <v>45900</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45808</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45716</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45626</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45535</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45443</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45351</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45260</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45169</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45077</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1858,10 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,323 +1875,379 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1389600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1363600</v>
+      </c>
+      <c r="F41" s="3">
         <v>2445900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2372600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1480600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1501400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2363700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2317500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1571700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1585800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2196300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2158200</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>31900</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>31300</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>57200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>58000</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>85400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>86200</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4964000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4871300</v>
+      </c>
+      <c r="F43" s="3">
         <v>4377100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>4246000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>4316900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>4377500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>4111300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>4031000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>4352000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>4390900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>3787400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3721600</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>372200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>365300</v>
+      </c>
+      <c r="F44" s="3">
         <v>355600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>344900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>349600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>354500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>356200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>349200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>347000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>350100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>351400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>345300</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>31300</v>
+      </c>
+      <c r="F45" s="3">
         <v>17500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>17000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>19800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>20000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>47600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>46600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>10800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>10900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>5787400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>5686900</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7054200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>6922500</v>
+      </c>
+      <c r="F46" s="3">
         <v>7398500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>7176900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>6436400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>6526700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>7075500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>6937400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>6622000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>6681200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>12351400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>12136800</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>547100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>536900</v>
+      </c>
+      <c r="F47" s="3">
         <v>314700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>305200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>476500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>483200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>297500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>291700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1274500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1285900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1074800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1056200</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1365900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1340400</v>
+      </c>
+      <c r="F48" s="3">
         <v>1388500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1346900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1350500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1369500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1354900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1328500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1366300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1378600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1406700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1382300</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7193700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>7059400</v>
+      </c>
+      <c r="F49" s="3">
         <v>6914300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>6707100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>6553900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>6645900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>6636400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>6506900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>6531200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>6589600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>6524900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>6411600</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2281,14 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,43 +2322,55 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1108400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1087700</v>
+      </c>
+      <c r="F52" s="3">
         <v>1055100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1023500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>880200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>892600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>940200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>921800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>826900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>834300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>902400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>886700</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,43 +2404,55 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17487900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>17161400</v>
+      </c>
+      <c r="F54" s="3">
         <v>17369300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>16849000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>15957800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>16181700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>16617600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>16293200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>16858700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>17009500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>22553100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>22161400</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2466,10 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,218 +2483,256 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3169100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3109900</v>
+      </c>
+      <c r="F57" s="3">
         <v>3065900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2974000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2843600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2883500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2889100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2832700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2788900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2813800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2713700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2666500</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1142600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1121300</v>
+      </c>
+      <c r="F58" s="3">
         <v>1140500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1106300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>942700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>955900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>967800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>948900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>225900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>227900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>743000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>730000</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>964200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>946200</v>
+      </c>
+      <c r="F59" s="3">
         <v>931100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>903200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>788700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>799700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1117100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1095300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>942600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>951000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>5594400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>5497200</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6925400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6796200</v>
+      </c>
+      <c r="F60" s="3">
         <v>6828900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6624300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5984800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6068800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>6550200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6422300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>5412400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>5460800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>10629100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>10444400</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5245200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5147300</v>
+      </c>
+      <c r="F61" s="3">
         <v>5229900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>5073200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>4890200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>4958900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>5079100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>4979900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>5808000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>5860000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>6224500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>6116400</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>522300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>512500</v>
+      </c>
+      <c r="F62" s="3">
         <v>410600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>398300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>348600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>353500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>319700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>313400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>338300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>341400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>308000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>302700</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2766,14 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2807,14 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,43 +2848,55 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13223400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>12976600</v>
+      </c>
+      <c r="F66" s="3">
         <v>12925500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>12538300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>11775000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>11940300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>12416800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>12174400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>12070000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>12178000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>17613900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>17307900</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2910,10 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2947,14 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2988,14 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2694,8 +3029,14 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,8 +3070,14 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -2764,8 +3111,14 @@
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +3152,14 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3193,14 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,43 +3234,55 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4252600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4173200</v>
+      </c>
+      <c r="F76" s="3">
         <v>4428600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4295900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4160900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4219200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4183200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4101500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>4770300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4813000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4926200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4840700</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,48 +3316,60 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45991</v>
+      </c>
+      <c r="F80" s="2">
         <v>45900</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45808</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45716</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45626</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45535</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45443</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45351</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45260</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45169</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45077</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3014,8 +3403,14 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,43 +3424,51 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>112900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>114500</v>
+      </c>
+      <c r="F83" s="3">
         <v>79100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>77500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>117800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>118900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>85700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>84200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>111500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>108300</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3502,14 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3543,14 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3584,14 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3625,14 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,43 +3666,55 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F89" s="3">
         <v>560300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>543500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>3100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>3200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>554100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>543300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>171900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>173400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>581300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>571200</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,43 +3728,51 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-102800</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-100900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-98800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-95900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-85300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-86500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-97900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-96000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-97800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-98700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-95400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-93800</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3806,14 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,43 +3847,55 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-242200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-237700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-106400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-103300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-108200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-109700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>421400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>413200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-977700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-986500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-130700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-128400</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,43 +3909,51 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>232800</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>228400</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>201900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>204700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>507100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>497200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>246500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>248700</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3987,14 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +4028,14 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,109 +4069,133 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-299500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-293900</v>
+      </c>
+      <c r="F100" s="3">
         <v>15200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>14800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-289300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-293300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-576800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-565600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-167000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-168500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-66700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-65500</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E101" s="3">
+        <v>23200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-17700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-17400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>8100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>8200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-49300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-48500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-53100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-51600</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-540600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-530500</v>
+      </c>
+      <c r="F102" s="3">
         <v>391900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>380100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-371400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-376700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>381000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>373600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-964800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-973400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>334600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>328800</v>
       </c>
     </row>
